--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/IDAHO_2018.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/IDAHO_2018.xlsx
@@ -1500,7 +1500,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C64">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C160">
@@ -8664,7 +8664,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C462">
